--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B266648D-8AF5-3642-B03F-728F27D38FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3C35D-C4B7-F94D-B521-0ABF1E45F34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-600" windowWidth="38400" windowHeight="20980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-620" windowWidth="35700" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">cost_factors!$A$1:$L$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">transformation_costs!$A$1:$O$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -6215,6 +6214,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -6239,7 +6241,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6249,18 +6251,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6296,15 +6286,14 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10726,12 +10715,11 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -11028,6 +11016,166 @@
       </c>
       <c r="B37">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.68846153799999987</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.67692307599999979</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.66538461399999971</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.65384615199999963</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.64230768999999954</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.63076922799999946</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.61923076599999938</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.60769230399999929</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.59615384199999921</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.58461537999999913</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.57307691799999905</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.56153845599999896</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.54999999399999888</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.5384615319999988</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.52692306999999872</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.51538460799999863</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.50384614599999855</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.49230768399999847</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.48076922199999839</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.4692307599999983</v>
       </c>
     </row>
   </sheetData>
@@ -14988,7 +15136,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -15290,6 +15438,166 @@
       </c>
       <c r="B37">
         <v>2050</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>2070</v>
       </c>
     </row>
   </sheetData>
@@ -16388,8 +16696,9 @@
   <cols>
     <col min="1" max="1" width="58.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.5" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
     <col min="8" max="8" width="41.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17192,15 +17501,14 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>467</v>
       </c>
-      <c r="C22" s="4">
-        <f>-86/3</f>
-        <v>-28.666666666666668</v>
+      <c r="C22">
+        <v>-86</v>
       </c>
       <c r="D22" t="s">
         <v>591</v>
@@ -17231,15 +17539,14 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" t="s">
         <v>468</v>
       </c>
-      <c r="C23" s="4">
-        <f>-61/3</f>
-        <v>-20.333333333333332</v>
+      <c r="C23">
+        <v>-61</v>
       </c>
       <c r="D23" t="s">
         <v>591</v>
@@ -17270,15 +17577,14 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" t="s">
         <v>469</v>
       </c>
-      <c r="C24" s="4">
-        <f>-70/3</f>
-        <v>-23.333333333333332</v>
+      <c r="C24">
+        <v>-70</v>
       </c>
       <c r="D24" t="s">
         <v>591</v>
@@ -17309,15 +17615,14 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" t="s">
         <v>470</v>
       </c>
-      <c r="C25" s="4">
-        <f>-57/3</f>
-        <v>-19</v>
+      <c r="C25">
+        <v>-57</v>
       </c>
       <c r="D25" t="s">
         <v>591</v>
@@ -17348,15 +17653,14 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" t="s">
         <v>471</v>
       </c>
-      <c r="C26" s="4">
-        <f>-7/3</f>
-        <v>-2.3333333333333335</v>
+      <c r="C26">
+        <v>-7</v>
       </c>
       <c r="D26" t="s">
         <v>591</v>
@@ -17387,15 +17691,14 @@
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
+      <c r="A27" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" t="s">
         <v>472</v>
       </c>
-      <c r="C27" s="4">
-        <f>-72/3</f>
-        <v>-24</v>
+      <c r="C27">
+        <v>-72</v>
       </c>
       <c r="D27" t="s">
         <v>591</v>
@@ -17426,15 +17729,14 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+      <c r="A28" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" t="s">
         <v>473</v>
       </c>
-      <c r="C28" s="4">
-        <f>-3.04/3</f>
-        <v>-1.0133333333333334</v>
+      <c r="C28">
+        <v>-3.04</v>
       </c>
       <c r="D28" t="s">
         <v>592</v>
@@ -17465,15 +17767,14 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" t="s">
         <v>474</v>
       </c>
-      <c r="C29" s="4">
-        <f>-3.04/3</f>
-        <v>-1.0133333333333334</v>
+      <c r="C29">
+        <v>-3.04</v>
       </c>
       <c r="D29" t="s">
         <v>592</v>
@@ -17504,15 +17805,14 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="A30" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" t="s">
         <v>475</v>
       </c>
-      <c r="C30" s="4">
-        <f>-0.64/3</f>
-        <v>-0.21333333333333335</v>
+      <c r="C30">
+        <v>-0.64</v>
       </c>
       <c r="D30" t="s">
         <v>592</v>
@@ -17543,15 +17843,14 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
+      <c r="A31" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" t="s">
         <v>476</v>
       </c>
-      <c r="C31" s="4">
-        <f>-1.44/3</f>
-        <v>-0.48</v>
+      <c r="C31">
+        <v>-1.44</v>
       </c>
       <c r="D31" t="s">
         <v>592</v>
@@ -17582,15 +17881,14 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>477</v>
       </c>
-      <c r="C32" s="4">
-        <f>-1.44/3</f>
-        <v>-0.48</v>
+      <c r="C32">
+        <v>-1.44</v>
       </c>
       <c r="D32" t="s">
         <v>592</v>
@@ -17621,15 +17919,14 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
+      <c r="A33" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" t="s">
         <v>478</v>
       </c>
-      <c r="C33" s="4">
-        <f>-0.06/3</f>
-        <v>-0.02</v>
+      <c r="C33">
+        <v>-0.06</v>
       </c>
       <c r="D33" t="s">
         <v>592</v>
@@ -18534,15 +18831,14 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
+      <c r="A57" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" t="s">
         <v>502</v>
       </c>
-      <c r="C57" s="4">
-        <f>-500/3</f>
-        <v>-166.66666666666666</v>
+      <c r="C57">
+        <v>-500</v>
       </c>
       <c r="D57" t="s">
         <v>595</v>
@@ -18611,14 +18907,14 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+      <c r="A59" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" t="s">
         <v>503</v>
       </c>
-      <c r="C59" s="3">
-        <v>-500</v>
+      <c r="C59">
+        <v>-500000</v>
       </c>
       <c r="D59" t="s">
         <v>353</v>
@@ -19334,15 +19630,14 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
+      <c r="A78" t="s">
         <v>81</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" t="s">
         <v>520</v>
       </c>
-      <c r="C78" s="4">
-        <f>-170/3</f>
-        <v>-56.666666666666664</v>
+      <c r="C78">
+        <v>-170</v>
       </c>
       <c r="D78" t="s">
         <v>591</v>
@@ -19373,15 +19668,14 @@
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
+      <c r="A79" t="s">
         <v>82</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" t="s">
         <v>521</v>
       </c>
-      <c r="C79" s="4">
-        <f>-500/3</f>
-        <v>-166.66666666666666</v>
+      <c r="C79">
+        <v>-500</v>
       </c>
       <c r="D79" t="s">
         <v>599</v>
@@ -19412,15 +19706,14 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
+      <c r="A80" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" t="s">
         <v>522</v>
       </c>
-      <c r="C80" s="4">
-        <f>-500/3</f>
-        <v>-166.66666666666666</v>
+      <c r="C80">
+        <v>-500</v>
       </c>
       <c r="D80" t="s">
         <v>599</v>
@@ -19793,15 +20086,14 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
+      <c r="A90" t="s">
         <v>93</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" t="s">
         <v>467</v>
       </c>
-      <c r="C90" s="4">
-        <f>-86/3</f>
-        <v>-28.666666666666668</v>
+      <c r="C90">
+        <v>-86</v>
       </c>
       <c r="D90" t="s">
         <v>591</v>
@@ -19832,15 +20124,14 @@
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A91" s="4" t="s">
+      <c r="A91" t="s">
         <v>94</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" t="s">
         <v>468</v>
       </c>
-      <c r="C91" s="4">
-        <f>-86/3</f>
-        <v>-28.666666666666668</v>
+      <c r="C91">
+        <v>-86</v>
       </c>
       <c r="D91" t="s">
         <v>591</v>
@@ -19871,15 +20162,14 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
+      <c r="A92" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" t="s">
         <v>469</v>
       </c>
-      <c r="C92" s="4">
-        <f>-86/3</f>
-        <v>-28.666666666666668</v>
+      <c r="C92">
+        <v>-86</v>
       </c>
       <c r="D92" t="s">
         <v>591</v>
@@ -19910,15 +20200,14 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A93" s="4" t="s">
+      <c r="A93" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" t="s">
         <v>470</v>
       </c>
-      <c r="C93" s="4">
-        <f>-86/3</f>
-        <v>-28.666666666666668</v>
+      <c r="C93">
+        <v>-86</v>
       </c>
       <c r="D93" t="s">
         <v>591</v>
@@ -19949,15 +20238,14 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
+      <c r="A94" t="s">
         <v>97</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" t="s">
         <v>471</v>
       </c>
-      <c r="C94" s="4">
-        <f>-60.2/3</f>
-        <v>-20.066666666666666</v>
+      <c r="C94">
+        <v>-60.2</v>
       </c>
       <c r="D94" t="s">
         <v>591</v>
@@ -19988,15 +20276,14 @@
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="4" t="s">
+      <c r="A95" t="s">
         <v>98</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" t="s">
         <v>472</v>
       </c>
-      <c r="C95" s="4">
-        <f>-60.2/3</f>
-        <v>-20.066666666666666</v>
+      <c r="C95">
+        <v>-60.2</v>
       </c>
       <c r="D95" t="s">
         <v>591</v>
@@ -21395,15 +21682,14 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A132" s="4" t="s">
+      <c r="A132" t="s">
         <v>135</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" t="s">
         <v>558</v>
       </c>
-      <c r="C132" s="4">
-        <f>-500000/5</f>
-        <v>-100000</v>
+      <c r="C132">
+        <v>-500000</v>
       </c>
       <c r="D132" t="s">
         <v>353</v>
@@ -22521,7 +22807,6 @@
     <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="131.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -22806,97 +23091,97 @@
         <v>816</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>728</v>
       </c>
-      <c r="C7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" t="s">
         <v>762</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" t="s">
         <v>764</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" t="s">
         <v>766</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" t="s">
         <v>780</v>
       </c>
-      <c r="I7" s="5">
-        <v>-8340</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="I7">
+        <v>-83400</v>
+      </c>
+      <c r="J7" t="s">
         <v>588</v>
       </c>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
         <v>353</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7">
         <v>99</v>
       </c>
-      <c r="N7" s="5" t="b">
+      <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>729</v>
       </c>
-      <c r="C8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" t="s">
         <v>762</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" t="s">
         <v>764</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" t="s">
         <v>766</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" t="s">
         <v>780</v>
       </c>
-      <c r="I8" s="5">
-        <v>100000</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8">
+        <v>10000000</v>
+      </c>
+      <c r="J8" t="s">
         <v>588</v>
       </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
         <v>353</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8">
         <v>99</v>
       </c>
-      <c r="N8" s="5" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" t="s">
         <v>817</v>
       </c>
     </row>
@@ -22994,50 +23279,50 @@
         <v>819</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>173</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>731</v>
       </c>
-      <c r="C11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>99</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" t="s">
         <v>762</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" t="s">
         <v>764</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" t="s">
         <v>766</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" t="s">
         <v>782</v>
       </c>
-      <c r="I11" s="5">
-        <v>-42240000</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="I11">
+        <v>-422400000</v>
+      </c>
+      <c r="J11" t="s">
         <v>588</v>
       </c>
-      <c r="K11" s="5">
-        <v>1</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
         <v>353</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11">
         <v>99</v>
       </c>
-      <c r="N11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="5" t="s">
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
         <v>820</v>
       </c>
     </row>
@@ -23276,332 +23561,332 @@
         <v>825</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>179</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" t="s">
         <v>734</v>
       </c>
-      <c r="C17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>99</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" t="s">
         <v>762</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" t="s">
         <v>764</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" t="s">
         <v>766</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" t="s">
         <v>785</v>
       </c>
-      <c r="I17" s="5">
-        <v>88000</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="I17">
+        <v>880000</v>
+      </c>
+      <c r="J17" t="s">
         <v>588</v>
       </c>
-      <c r="K17" s="5">
-        <v>1</v>
-      </c>
-      <c r="L17" s="5" t="s">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" t="s">
         <v>353</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17">
         <v>99</v>
       </c>
-      <c r="N17" s="5" t="b">
+      <c r="N17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="5" t="s">
+      <c r="O17" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>180</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" t="s">
         <v>735</v>
       </c>
-      <c r="C18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18">
         <v>99</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" t="s">
         <v>762</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" t="s">
         <v>764</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" t="s">
         <v>768</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" t="s">
         <v>785</v>
       </c>
-      <c r="I18" s="5">
-        <v>88000</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="I18">
+        <v>880000</v>
+      </c>
+      <c r="J18" t="s">
         <v>588</v>
       </c>
-      <c r="K18" s="5">
-        <v>1</v>
-      </c>
-      <c r="L18" s="5" t="s">
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" t="s">
         <v>809</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18">
         <v>0</v>
       </c>
-      <c r="N18" s="5" t="b">
+      <c r="N18" t="b">
         <v>0</v>
       </c>
-      <c r="O18" s="5" t="s">
+      <c r="O18" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="19" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>181</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" t="s">
         <v>735</v>
       </c>
-      <c r="C19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <v>99</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" t="s">
         <v>762</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" t="s">
         <v>764</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" t="s">
         <v>768</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" t="s">
         <v>785</v>
       </c>
-      <c r="I19" s="5">
-        <v>88000</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I19">
+        <v>880000</v>
+      </c>
+      <c r="J19" t="s">
         <v>588</v>
       </c>
-      <c r="K19" s="5">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5" t="s">
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19" t="s">
         <v>809</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19">
         <v>0</v>
       </c>
-      <c r="N19" s="5" t="b">
+      <c r="N19" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="5" t="s">
+      <c r="O19" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>182</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>736</v>
       </c>
-      <c r="C20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <v>99</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" t="s">
         <v>762</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" t="s">
         <v>764</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" t="s">
         <v>766</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" t="s">
         <v>786</v>
       </c>
-      <c r="I20" s="5">
-        <v>556000</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="I20">
+        <v>5560000</v>
+      </c>
+      <c r="J20" t="s">
         <v>588</v>
       </c>
-      <c r="K20" s="5">
-        <v>1</v>
-      </c>
-      <c r="L20" s="5" t="s">
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20" t="s">
         <v>353</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20">
         <v>99</v>
       </c>
-      <c r="N20" s="5" t="b">
+      <c r="N20" t="b">
         <v>0</v>
       </c>
-      <c r="O20" s="5" t="s">
+      <c r="O20" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="21" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>183</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" t="s">
         <v>737</v>
       </c>
-      <c r="C21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <v>99</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" t="s">
         <v>762</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" t="s">
         <v>764</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" t="s">
         <v>766</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" t="s">
         <v>786</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21">
         <v>463333.3333</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" t="s">
         <v>588</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21">
         <v>0.88719309999999996</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L21" t="s">
         <v>353</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21">
         <v>99</v>
       </c>
-      <c r="N21" s="5" t="b">
+      <c r="N21" t="b">
         <v>0</v>
       </c>
-      <c r="O21" s="5" t="s">
+      <c r="O21" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>184</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" t="s">
         <v>737</v>
       </c>
-      <c r="C22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22">
         <v>99</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" t="s">
         <v>762</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" t="s">
         <v>764</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" t="s">
         <v>766</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" t="s">
         <v>786</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22">
         <v>-83400</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" t="s">
         <v>588</v>
       </c>
-      <c r="K22" s="5">
-        <v>1</v>
-      </c>
-      <c r="L22" s="5" t="s">
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
         <v>353</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22">
         <v>99</v>
       </c>
-      <c r="N22" s="5" t="b">
+      <c r="N22" t="b">
         <v>0</v>
       </c>
-      <c r="O22" s="5" t="s">
+      <c r="O22" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="23" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>185</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" t="s">
         <v>738</v>
       </c>
-      <c r="C23" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <v>99</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" t="s">
         <v>762</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" t="s">
         <v>764</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" t="s">
         <v>766</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" t="s">
         <v>786</v>
       </c>
-      <c r="I23" s="5">
-        <v>556000</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="I23">
+        <v>5560000</v>
+      </c>
+      <c r="J23" t="s">
         <v>588</v>
       </c>
-      <c r="K23" s="5">
-        <v>1</v>
-      </c>
-      <c r="L23" s="5" t="s">
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23" t="s">
         <v>353</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23">
         <v>99</v>
       </c>
-      <c r="N23" s="5" t="b">
+      <c r="N23" t="b">
         <v>0</v>
       </c>
-      <c r="O23" s="5" t="s">
+      <c r="O23" t="s">
         <v>827</v>
       </c>
     </row>
@@ -24876,7 +25161,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O50" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -25448,12 +25732,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -25748,8 +26033,168 @@
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37">
-        <v>0.55000000000000004</v>
+      <c r="B37" s="4">
+        <v>0.54999999899999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4">
+        <v>0.53269230599999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0.51538461299999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0.49807691999999992</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0.48076922699999991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0.4634615339999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4">
+        <v>0.44615384099999988</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4">
+        <v>0.42884614799999987</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0.41153845499999986</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" s="4">
+        <v>0.39423076199999985</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4">
+        <v>0.37692306899999983</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4">
+        <v>0.35961537599999982</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4">
+        <v>0.34230768299999981</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4">
+        <v>0.32499998999999979</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4">
+        <v>0.30769229699999978</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4">
+        <v>0.29038460399999977</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" s="4">
+        <v>0.27307691099999976</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" s="4">
+        <v>0.25576921799999974</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" s="4">
+        <v>0.23846152499999973</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" s="4">
+        <v>0.22115383199999972</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" s="4">
+        <v>0.2038461389999997</v>
       </c>
     </row>
   </sheetData>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3C35D-C4B7-F94D-B521-0ABF1E45F34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52F7B94-6991-6F4D-91BA-BDB3CE34D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-620" windowWidth="35700" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43180" yWindow="-7160" windowWidth="40760" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -17007,7 +17007,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
@@ -17045,7 +17045,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52F7B94-6991-6F4D-91BA-BDB3CE34D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F76EA8-D4B6-984E-9B59-936290BF019F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-43180" yWindow="-7160" windowWidth="40760" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -17729,14 +17729,15 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C28">
-        <v>-3.04</v>
+      <c r="C28" s="3">
+        <f>-3.04/3</f>
+        <v>-1.0133333333333334</v>
       </c>
       <c r="D28" t="s">
         <v>592</v>
@@ -17767,14 +17768,15 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C29">
-        <v>-3.04</v>
+      <c r="C29" s="3">
+        <f>-3.04/3</f>
+        <v>-1.0133333333333334</v>
       </c>
       <c r="D29" t="s">
         <v>592</v>
@@ -18831,14 +18833,14 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="A57" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="C57">
-        <v>-500</v>
+      <c r="C57" s="3">
+        <v>-50</v>
       </c>
       <c r="D57" t="s">
         <v>595</v>

--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_mexico/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F76EA8-D4B6-984E-9B59-936290BF019F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94383122-9CB6-EF41-86A7-2C6AFDCB6179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-620" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-7160" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -26449,10 +26449,12 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26493,7 +26495,7 @@
         <v>508</v>
       </c>
       <c r="B2">
-        <v>-40</v>
+        <v>-55</v>
       </c>
       <c r="C2" t="s">
         <v>596</v>
@@ -26525,7 +26527,7 @@
         <v>888</v>
       </c>
       <c r="B3">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="C3" t="s">
         <v>596</v>
@@ -26557,7 +26559,7 @@
         <v>515</v>
       </c>
       <c r="B4">
-        <v>-50</v>
+        <v>-65</v>
       </c>
       <c r="C4" t="s">
         <v>596</v>
@@ -26589,7 +26591,7 @@
         <v>889</v>
       </c>
       <c r="B5">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="C5" t="s">
         <v>596</v>
